--- a/data/trans_orig/P32-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P32-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han pensado que deberían beber menos en 2007</t>
+          <t>Población según si han pensado que deberían beber menos en 2007 (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11545</t>
+          <t>12454</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7442</t>
+          <t>5997</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3744</t>
+          <t>2896</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14216</t>
+          <t>14752</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>134604</t>
+          <t>133695</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>144242</t>
+          <t>144147</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>66034</t>
+          <t>67479</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>205409</t>
+          <t>204873</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>215881</t>
+          <t>216729</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7181</t>
+          <t>7907</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20687</t>
+          <t>22669</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5025</t>
+          <t>4448</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7986</t>
+          <t>8102</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23169</t>
+          <t>22541</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,47%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>208130</t>
+          <t>206148</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>221636</t>
+          <t>220910</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>67726</t>
+          <t>68303</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>278399</t>
+          <t>279027</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>293582</t>
+          <t>293466</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,31%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4514</t>
+          <t>5027</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,47 +1454,47 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>996</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>1872</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>996</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4999</t>
+          <t>4991</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>189426</t>
+          <t>188913</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>85097</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>86969</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>275910</t>
+          <t>275918</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5501</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20458</t>
+          <t>20380</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>1174</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11778</t>
+          <t>11215</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9436</t>
+          <t>9304</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25740</t>
+          <t>25792</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>217437</t>
+          <t>217515</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>232394</t>
+          <t>232304</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>119148</t>
+          <t>119711</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>129746</t>
+          <t>129752</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>343082</t>
+          <t>343030</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>359386</t>
+          <t>359518</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,48%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>831</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7044</t>
+          <t>6959</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8143</t>
+          <t>7503</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>923</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11247</t>
+          <t>10566</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,38%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>89854</t>
+          <t>89939</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>96086</t>
+          <t>96067</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>38214</t>
+          <t>38854</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>132008</t>
+          <t>132689</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>142322</t>
+          <t>142332</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,36%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1031</t>
+          <t>1736</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11431</t>
+          <t>12406</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6117</t>
+          <t>6091</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2778</t>
+          <t>2821</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13249</t>
+          <t>14025</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>182853</t>
+          <t>181878</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>193253</t>
+          <t>192548</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>105666</t>
+          <t>105692</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>292818</t>
+          <t>292042</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>303289</t>
+          <t>303246</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1881</t>
+          <t>1824</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11463</t>
+          <t>12761</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1923</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1769</t>
+          <t>1847</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11233</t>
+          <t>11967</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>278570</t>
+          <t>277272</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>288152</t>
+          <t>288209</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>130458</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>132381</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>411181</t>
+          <t>410447</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>420645</t>
+          <t>420567</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,56%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3550</t>
+          <t>3526</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>16037</t>
+          <t>15895</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6811</t>
+          <t>6481</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4811</t>
+          <t>5156</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>18691</t>
+          <t>18748</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>476851</t>
+          <t>476993</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>489338</t>
+          <t>489362</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>233127</t>
+          <t>233457</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>714135</t>
+          <t>714078</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>728015</t>
+          <t>727670</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>39191</t>
+          <t>38924</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>69535</t>
+          <t>66093</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>6959</t>
+          <t>7108</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>22689</t>
+          <t>22856</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>50238</t>
+          <t>50788</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>82102</t>
+          <t>83364</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1811369</t>
+          <t>1814811</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1841713</t>
+          <t>1841980</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>871892</t>
+          <t>871725</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>887622</t>
+          <t>887473</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2693384</t>
+          <t>2692122</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2725248</t>
+          <t>2724698</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,17%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han pensado que deberían beber menos en 2012</t>
+          <t>Población según si han pensado que deberían beber menos en 2012 (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32466</t>
+          <t>31306</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55601</t>
+          <t>55914</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1844</t>
+          <t>1840</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16008</t>
+          <t>14657</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36712</t>
+          <t>37352</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>63169</t>
+          <t>65189</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,96%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>119724</t>
+          <t>119411</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>142859</t>
+          <t>144019</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>68,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>92646</t>
+          <t>93997</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>106810</t>
+          <t>106814</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>220809</t>
+          <t>218789</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>247266</t>
+          <t>246626</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>86,85%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18182</t>
+          <t>17317</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39737</t>
+          <t>39252</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9607</t>
+          <t>9739</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20981</t>
+          <t>21140</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44021</t>
+          <t>44602</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,66%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>270383</t>
+          <t>270868</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>291938</t>
+          <t>292803</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>141755</t>
+          <t>141623</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>150369</t>
+          <t>150361</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>417461</t>
+          <t>416880</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>440501</t>
+          <t>440342</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,42%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>955</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9826</t>
+          <t>8949</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4925</t>
+          <t>5041</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>1886</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10631</t>
+          <t>10539</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>192647</t>
+          <t>193524</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>201446</t>
+          <t>201518</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>119724</t>
+          <t>119608</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>316491</t>
+          <t>316583</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>325240</t>
+          <t>325236</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3094</t>
+          <t>3636</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18170</t>
+          <t>16132</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5125,7 +5125,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>5595</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4839</t>
+          <t>4800</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18575</t>
+          <t>17943</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>171998</t>
+          <t>174036</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>187074</t>
+          <t>186532</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>80896</t>
+          <t>81747</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>258935</t>
+          <t>259567</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>272671</t>
+          <t>272710</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5447</t>
+          <t>5945</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18378</t>
+          <t>19861</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4513</t>
+          <t>4700</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6564</t>
+          <t>6180</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20179</t>
+          <t>21022</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,53%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>109830</t>
+          <t>108347</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>122761</t>
+          <t>122263</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>49596</t>
+          <t>49409</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>162138</t>
+          <t>161295</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>175753</t>
+          <t>176137</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,61%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2875</t>
+          <t>2320</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14176</t>
+          <t>12927</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4803</t>
+          <t>5189</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3049</t>
+          <t>3283</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14893</t>
+          <t>15023</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>170071</t>
+          <t>171320</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>181372</t>
+          <t>181927</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>89403</t>
+          <t>89017</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>263560</t>
+          <t>263430</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>275404</t>
+          <t>275170</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,82%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11653</t>
+          <t>12559</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29421</t>
+          <t>31604</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>986</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8451</t>
+          <t>9008</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14436</t>
+          <t>14562</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>33253</t>
+          <t>34855</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>368048</t>
+          <t>365865</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>385816</t>
+          <t>384910</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>206074</t>
+          <t>205517</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>213553</t>
+          <t>213539</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>578742</t>
+          <t>577140</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>597559</t>
+          <t>597433</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,62%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10640</t>
+          <t>11085</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>29600</t>
+          <t>30145</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10766</t>
+          <t>9929</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>14793</t>
+          <t>14737</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>35830</t>
+          <t>35462</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>423009</t>
+          <t>422464</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>441969</t>
+          <t>441524</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>205195</t>
+          <t>206032</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>214900</t>
+          <t>214859</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>632741</t>
+          <t>633109</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>653778</t>
+          <t>653834</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,8%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>114844</t>
+          <t>115514</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>161660</t>
+          <t>162242</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>14266</t>
+          <t>13863</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>35088</t>
+          <t>34593</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>136494</t>
+          <t>133873</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>189385</t>
+          <t>187440</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1878959</t>
+          <t>1878377</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1925775</t>
+          <t>1925105</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1015720</t>
+          <t>1016215</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1036542</t>
+          <t>1036945</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2902042</t>
+          <t>2903987</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2954933</t>
+          <t>2957554</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,67%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han pensado que deberían beber menos en 2016</t>
+          <t>Población según si han pensado que deberían beber menos en 2016 (tasa de respuesta: 99,53%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18905</t>
+          <t>17903</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39470</t>
+          <t>39998</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3791</t>
+          <t>4454</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16260</t>
+          <t>15286</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25939</t>
+          <t>26016</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49429</t>
+          <t>50234</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,76%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>139202</t>
+          <t>138674</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>159767</t>
+          <t>160769</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>87859</t>
+          <t>88833</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>100328</t>
+          <t>99665</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>233363</t>
+          <t>232558</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>256853</t>
+          <t>256776</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,8%</t>
         </is>
       </c>
     </row>
@@ -7727,7 +7727,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9840</t>
+          <t>9135</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6309</t>
+          <t>6517</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>1132</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11255</t>
+          <t>10403</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -7835,7 +7835,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>257898</t>
+          <t>258603</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>95950</t>
+          <t>95742</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7885,7 +7885,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>358742</t>
+          <t>359594</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>368866</t>
+          <t>368865</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1857</t>
+          <t>1725</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10829</t>
+          <t>9468</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4206</t>
+          <t>3942</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1821</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11074</t>
+          <t>11838</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>193348</t>
+          <t>194709</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>202320</t>
+          <t>202452</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>118272</t>
+          <t>118536</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>315581</t>
+          <t>314817</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>324834</t>
+          <t>324639</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4323</t>
+          <t>4482</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17679</t>
+          <t>17037</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8448,7 +8448,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9532</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6339</t>
+          <t>6639</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21664</t>
+          <t>21692</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>215730</t>
+          <t>216372</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>229086</t>
+          <t>228927</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>141485</t>
+          <t>142110</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>362762</t>
+          <t>362734</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>378087</t>
+          <t>377787</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8611,7 +8611,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>909</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6877</t>
+          <t>7606</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1746</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>933</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7752</t>
+          <t>7666</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>83412</t>
+          <t>82683</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>89367</t>
+          <t>89380</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35728</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>37474</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>120012</t>
+          <t>120098</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>126827</t>
+          <t>126831</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1875</t>
+          <t>1885</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10675</t>
+          <t>10592</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6113</t>
+          <t>6686</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2868</t>
+          <t>2841</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12592</t>
+          <t>14226</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>178378</t>
+          <t>178461</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>187178</t>
+          <t>187168</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>98615</t>
+          <t>98042</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>281189</t>
+          <t>279555</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>290913</t>
+          <t>290940</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,03%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>26224</t>
+          <t>25433</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>51299</t>
+          <t>50940</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>11628</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>27949</t>
+          <t>28963</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>41016</t>
+          <t>42925</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>72703</t>
+          <t>70965</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,1%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>329173</t>
+          <t>329532</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>354248</t>
+          <t>355039</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>231015</t>
+          <t>230001</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>247795</t>
+          <t>247336</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>566733</t>
+          <t>568471</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>598420</t>
+          <t>596511</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,29%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8203</t>
+          <t>7997</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23308</t>
+          <t>23039</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1113</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10322</t>
+          <t>11165</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>11256</t>
+          <t>10532</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>29124</t>
+          <t>28365</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>433118</t>
+          <t>433387</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>448223</t>
+          <t>448429</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>254946</t>
+          <t>254103</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>264155</t>
+          <t>264267</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>692569</t>
+          <t>693328</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>710437</t>
+          <t>711161</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,54%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>86191</t>
+          <t>85564</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>129082</t>
+          <t>128607</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>27059</t>
+          <t>26546</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>51661</t>
+          <t>51518</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>118964</t>
+          <t>117227</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>169567</t>
+          <t>165883</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1871154</t>
+          <t>1871629</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1914045</t>
+          <t>1914672</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1094646</t>
+          <t>1094789</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1119248</t>
+          <t>1119761</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2976976</t>
+          <t>2980660</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3027579</t>
+          <t>3029316</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,27%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han pensado que deberían beber menos en 2023</t>
+          <t>Población según si han pensado que deberían beber menos en 2023 (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3177</t>
+          <t>3274</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19501</t>
+          <t>18439</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3206</t>
+          <t>3011</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19286</t>
+          <t>18808</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>160388</t>
+          <t>161450</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>176712</t>
+          <t>176615</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>89622</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>90683</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>251286</t>
+          <t>251764</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>267366</t>
+          <t>267561</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,89%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>928</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12170</t>
+          <t>13039</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11085,7 +11085,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3064</t>
+          <t>3007</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11100,7 +11100,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1219</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11944</t>
+          <t>12442</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>242286</t>
+          <t>241417</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>253571</t>
+          <t>253528</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,7 +11193,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>113182</t>
+          <t>113239</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -11208,7 +11208,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>358759</t>
+          <t>358261</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>369424</t>
+          <t>369484</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,67%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11941</t>
+          <t>11659</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29484</t>
+          <t>28030</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>607</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5433</t>
+          <t>5887</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11443,7 +11443,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14193</t>
+          <t>13392</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31554</t>
+          <t>30572</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,1%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>155702</t>
+          <t>157156</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>173245</t>
+          <t>173527</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>84839</t>
+          <t>84385</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>89666</t>
+          <t>89665</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,7 +11551,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>243904</t>
+          <t>244886</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>261265</t>
+          <t>262066</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>95,14%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3815</t>
+          <t>3586</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16175</t>
+          <t>15696</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11771,7 +11771,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3306</t>
+          <t>3021</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11786,7 +11786,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4352</t>
+          <t>4419</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16647</t>
+          <t>16912</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>162003</t>
+          <t>162482</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>174363</t>
+          <t>174592</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>121039</t>
+          <t>121324</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -11894,7 +11894,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>285877</t>
+          <t>285612</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>298172</t>
+          <t>298105</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,54%</t>
         </is>
       </c>
     </row>
@@ -12074,97 +12074,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>440</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1267</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>2046</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>5,13%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,07%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>23,83%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>440</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2375</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>5,13%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>2490</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>27,67%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>440</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>2437</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29879</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31146</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,7 +12222,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6208</t>
+          <t>6537</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -12257,7 +12257,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37292</t>
+          <t>37239</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -12272,7 +12272,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5346</t>
+          <t>4902</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16256</t>
+          <t>16056</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>729</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6148</t>
+          <t>6260</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7099</t>
+          <t>6482</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19190</t>
+          <t>18566</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>148792</t>
+          <t>148992</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>159702</t>
+          <t>160146</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>90272</t>
+          <t>90160</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>95880</t>
+          <t>95691</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>242278</t>
+          <t>242902</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>254369</t>
+          <t>254986</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,52%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28774</t>
+          <t>29682</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>59851</t>
+          <t>62744</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3393</t>
+          <t>2867</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>36129</t>
+          <t>35268</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>23688</t>
+          <t>26236</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>91528</t>
+          <t>89247</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,6%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>248079</t>
+          <t>245186</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>279156</t>
+          <t>278248</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>364155</t>
+          <t>365016</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>396891</t>
+          <t>397417</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>616686</t>
+          <t>618967</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>684526</t>
+          <t>681978</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,3%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2790</t>
+          <t>2684</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12839</t>
+          <t>12351</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>990</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8419</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4946</t>
+          <t>4785</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>16739</t>
+          <t>17143</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>264698</t>
+          <t>265186</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>274747</t>
+          <t>274853</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>91406</t>
+          <t>91161</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>99091</t>
+          <t>98835</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>360623</t>
+          <t>360219</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>372416</t>
+          <t>372577</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,73%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>76577</t>
+          <t>77979</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>120635</t>
+          <t>121734</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>12219</t>
+          <t>12493</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>37688</t>
+          <t>37468</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>93260</t>
+          <t>93197</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>150209</t>
+          <t>150627</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13536,7 +13536,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1458736</t>
+          <t>1457637</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1502794</t>
+          <t>1501392</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>988971</t>
+          <t>989191</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1014440</t>
+          <t>1014166</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2455820</t>
+          <t>2455402</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2512769</t>
+          <t>2512832</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,7 +13644,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">

--- a/data/trans_orig/P32-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P32-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>1957</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12454</t>
+          <t>11699</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5997</t>
+          <t>6866</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2896</t>
+          <t>3339</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14752</t>
+          <t>14474</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>133695</t>
+          <t>134450</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>144147</t>
+          <t>144192</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>67479</t>
+          <t>66610</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>204873</t>
+          <t>205151</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>216729</t>
+          <t>216286</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,48%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7907</t>
+          <t>7065</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22669</t>
+          <t>20613</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4448</t>
+          <t>5843</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8102</t>
+          <t>8122</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22541</t>
+          <t>23532</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,8%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>206148</t>
+          <t>208204</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>220910</t>
+          <t>221752</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>68303</t>
+          <t>66908</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>279027</t>
+          <t>278036</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>293466</t>
+          <t>293446</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5027</t>
+          <t>5914</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4991</t>
+          <t>5662</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>188913</t>
+          <t>188026</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>275918</t>
+          <t>275247</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>5545</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20380</t>
+          <t>19605</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,82 +1777,82 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8,24%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>4741</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1172</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>11972</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>3,62%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>9,14%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>15857</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>8668</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>24899</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>4,3%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>2,35%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8,57%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>4741</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1174</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>11215</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>3,62%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>8,57%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>15857</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>9304</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>25792</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>4,3%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>217515</t>
+          <t>218290</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>232304</t>
+          <t>232350</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,82 +1890,82 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>97,67%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>126185</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>118954</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>129754</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>96,38%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>90,86%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>99,11%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>352965</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>343923</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>360154</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>95,7%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>93,25%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>97,65%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>126185</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>119711</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>129752</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>96,38%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>91,43%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,1%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>357</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>352965</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>343030</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>359518</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>95,7%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>93,01%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>97,48%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>816</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6959</t>
+          <t>7200</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7503</t>
+          <t>8065</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>907</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10566</t>
+          <t>10599</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,4%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>89939</t>
+          <t>89698</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>96067</t>
+          <t>96082</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>38854</t>
+          <t>38292</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>132689</t>
+          <t>132656</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>142332</t>
+          <t>142348</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,37%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12406</t>
+          <t>12509</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6091</t>
+          <t>5975</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2821</t>
+          <t>2863</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14025</t>
+          <t>14554</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>181878</t>
+          <t>181775</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>192548</t>
+          <t>193225</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>105692</t>
+          <t>105808</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>292042</t>
+          <t>291513</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>303246</t>
+          <t>303204</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1824</t>
+          <t>1839</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12761</t>
+          <t>12962</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1847</t>
+          <t>1783</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11967</t>
+          <t>12166</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>277272</t>
+          <t>277071</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>288209</t>
+          <t>288194</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>410447</t>
+          <t>410248</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>420567</t>
+          <t>420631</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,58%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3526</t>
+          <t>3536</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15895</t>
+          <t>16363</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6481</t>
+          <t>7803</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5156</t>
+          <t>5105</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>18748</t>
+          <t>17775</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>476993</t>
+          <t>476525</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>489362</t>
+          <t>489352</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>233457</t>
+          <t>232135</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>714078</t>
+          <t>715051</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>727670</t>
+          <t>727721</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>39033</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>66093</t>
+          <t>67920</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>7108</t>
+          <t>7166</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>22856</t>
+          <t>22250</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>50788</t>
+          <t>49996</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>83364</t>
+          <t>81576</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1814811</t>
+          <t>1812984</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1841980</t>
+          <t>1841871</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>871725</t>
+          <t>872331</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>887473</t>
+          <t>887415</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2692122</t>
+          <t>2693910</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2724698</t>
+          <t>2725490</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,2%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31306</t>
+          <t>31686</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55914</t>
+          <t>55222</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1840</t>
+          <t>1821</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14657</t>
+          <t>16708</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>37352</t>
+          <t>35651</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>65189</t>
+          <t>64626</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,76%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>119411</t>
+          <t>120103</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>144019</t>
+          <t>143639</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>68,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>93997</t>
+          <t>91946</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>106814</t>
+          <t>106833</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>218789</t>
+          <t>219352</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>246626</t>
+          <t>248327</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>87,45%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17317</t>
+          <t>17792</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39252</t>
+          <t>37926</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>998</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9739</t>
+          <t>9955</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21140</t>
+          <t>21618</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44602</t>
+          <t>45501</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,86%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>270868</t>
+          <t>272194</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>292803</t>
+          <t>292328</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>141623</t>
+          <t>141407</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>150361</t>
+          <t>150364</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>416880</t>
+          <t>415981</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>440342</t>
+          <t>439864</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,32%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>951</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8949</t>
+          <t>9373</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5041</t>
+          <t>5019</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>1895</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10539</t>
+          <t>11467</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>193524</t>
+          <t>193100</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>201518</t>
+          <t>201522</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>119608</t>
+          <t>119630</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>316583</t>
+          <t>315655</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>325236</t>
+          <t>325227</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3636</t>
+          <t>3873</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16132</t>
+          <t>16878</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5125,7 +5125,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5595</t>
+          <t>6030</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4800</t>
+          <t>4689</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17943</t>
+          <t>18549</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>174036</t>
+          <t>173290</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>186532</t>
+          <t>186295</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>81747</t>
+          <t>81312</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>259567</t>
+          <t>258961</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>272710</t>
+          <t>272821</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,31%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5945</t>
+          <t>5892</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19861</t>
+          <t>19266</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4700</t>
+          <t>5224</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6180</t>
+          <t>6883</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21022</t>
+          <t>20416</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,2%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>108347</t>
+          <t>108942</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>122263</t>
+          <t>122316</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>49409</t>
+          <t>48885</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>161295</t>
+          <t>161901</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>176137</t>
+          <t>175434</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,22%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2320</t>
+          <t>2416</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12927</t>
+          <t>13386</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5189</t>
+          <t>4714</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3283</t>
+          <t>2927</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15023</t>
+          <t>13478</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>171320</t>
+          <t>170861</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>181927</t>
+          <t>181831</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>89017</t>
+          <t>89492</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>263430</t>
+          <t>264975</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>275170</t>
+          <t>275526</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12559</t>
+          <t>11733</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>31604</t>
+          <t>31982</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>977</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9008</t>
+          <t>8960</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14562</t>
+          <t>14423</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>34855</t>
+          <t>35237</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>365865</t>
+          <t>365487</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>384910</t>
+          <t>385736</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>205517</t>
+          <t>205565</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>213539</t>
+          <t>213548</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>577140</t>
+          <t>576758</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>597433</t>
+          <t>597572</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,64%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11085</t>
+          <t>11326</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>30145</t>
+          <t>31451</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1057</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9929</t>
+          <t>10317</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>14737</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>35462</t>
+          <t>35641</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>422464</t>
+          <t>421158</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>441524</t>
+          <t>441283</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>206032</t>
+          <t>205644</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>214859</t>
+          <t>214904</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>633109</t>
+          <t>632930</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>653834</t>
+          <t>653730</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,78%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>115514</t>
+          <t>114463</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>162242</t>
+          <t>163599</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>13863</t>
+          <t>13739</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>34593</t>
+          <t>35819</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>133873</t>
+          <t>135889</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>187440</t>
+          <t>185844</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1878377</t>
+          <t>1877020</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1925105</t>
+          <t>1926156</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1016215</t>
+          <t>1014989</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1036945</t>
+          <t>1037069</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2903987</t>
+          <t>2905583</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2957554</t>
+          <t>2955538</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,6%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17903</t>
+          <t>18144</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39998</t>
+          <t>39798</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4454</t>
+          <t>3729</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15286</t>
+          <t>15690</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26016</t>
+          <t>25152</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>50234</t>
+          <t>49812</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,61%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>138674</t>
+          <t>138874</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>160769</t>
+          <t>160528</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>88833</t>
+          <t>88429</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>99665</t>
+          <t>100390</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>232558</t>
+          <t>232980</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>256776</t>
+          <t>257640</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>91,11%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9135</t>
+          <t>9531</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6517</t>
+          <t>4510</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10403</t>
+          <t>10904</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>258603</t>
+          <t>258207</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>266721</t>
+          <t>266723</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>95742</t>
+          <t>97749</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7885,7 +7885,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>359594</t>
+          <t>359093</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>368865</t>
+          <t>368862</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1725</t>
+          <t>1724</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9468</t>
+          <t>10200</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3942</t>
+          <t>4680</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>1966</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11838</t>
+          <t>11119</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>194709</t>
+          <t>193977</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>202452</t>
+          <t>202453</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>118536</t>
+          <t>117798</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>314817</t>
+          <t>315536</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>324639</t>
+          <t>324689</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,4%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4482</t>
+          <t>4602</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17037</t>
+          <t>17873</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8448,7 +8448,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>8748</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6639</t>
+          <t>6617</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21692</t>
+          <t>21649</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>216372</t>
+          <t>215536</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>228927</t>
+          <t>228807</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>142110</t>
+          <t>142269</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>362734</t>
+          <t>362777</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>377787</t>
+          <t>377809</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,28%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>933</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7606</t>
+          <t>7595</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>922</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7666</t>
+          <t>8536</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>82683</t>
+          <t>82694</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>89380</t>
+          <t>89356</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>120098</t>
+          <t>119228</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>126831</t>
+          <t>126842</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1885</t>
+          <t>1853</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10592</t>
+          <t>10760</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6686</t>
+          <t>5788</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2841</t>
+          <t>2863</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14226</t>
+          <t>12744</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>178461</t>
+          <t>178293</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>187168</t>
+          <t>187200</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>98042</t>
+          <t>98940</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>279555</t>
+          <t>281037</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>290940</t>
+          <t>290918</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25433</t>
+          <t>25030</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>50940</t>
+          <t>51156</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11628</t>
+          <t>11465</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>28963</t>
+          <t>27564</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>42925</t>
+          <t>42666</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>70965</t>
+          <t>71796</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,23%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>329532</t>
+          <t>329316</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>355039</t>
+          <t>355442</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>230001</t>
+          <t>231400</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>247336</t>
+          <t>247499</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>568471</t>
+          <t>567640</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>596511</t>
+          <t>596770</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,33%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7997</t>
+          <t>7838</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23039</t>
+          <t>23703</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1121</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11165</t>
+          <t>10370</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>10532</t>
+          <t>11651</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>28365</t>
+          <t>27934</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>433387</t>
+          <t>432723</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>448429</t>
+          <t>448588</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>254103</t>
+          <t>254898</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>264267</t>
+          <t>264147</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>693328</t>
+          <t>693759</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>711161</t>
+          <t>710042</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,39%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>85564</t>
+          <t>86421</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>128607</t>
+          <t>127534</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>26546</t>
+          <t>27421</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>51518</t>
+          <t>51923</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>117227</t>
+          <t>120909</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>165883</t>
+          <t>168154</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1871629</t>
+          <t>1872702</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1914672</t>
+          <t>1913815</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1094789</t>
+          <t>1094384</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1119761</t>
+          <t>1118886</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2980660</t>
+          <t>2978389</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3029316</t>
+          <t>3025634</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,16%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>8581</t>
+          <t>6867</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3274</t>
+          <t>2621</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18439</t>
+          <t>14904</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>8581</t>
+          <t>6867</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3011</t>
+          <t>2942</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18808</t>
+          <t>15393</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>171308</t>
+          <t>163032</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>161450</t>
+          <t>154995</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>176615</t>
+          <t>167278</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,7 +10845,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>90683</t>
+          <t>97231</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>261991</t>
+          <t>260263</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>251764</t>
+          <t>251737</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>267561</t>
+          <t>264188</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>179889</t>
+          <t>169899</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>179889</t>
+          <t>169899</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>179889</t>
+          <t>169899</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>90683</t>
+          <t>97231</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>90683</t>
+          <t>97231</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>90683</t>
+          <t>97231</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>270572</t>
+          <t>267130</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>270572</t>
+          <t>267130</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>270572</t>
+          <t>267130</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,22 +11040,22 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4169</t>
+          <t>4174</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>933</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13039</t>
+          <t>12565</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -11065,7 +11065,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,7 +11075,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>602</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -11085,12 +11085,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3007</t>
+          <t>3378</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -11100,7 +11100,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>4756</t>
+          <t>4776</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1219</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12442</t>
+          <t>13480</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -11153,27 +11153,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>250287</t>
+          <t>254537</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>241417</t>
+          <t>246146</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>253528</t>
+          <t>257778</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -11188,27 +11188,27 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>115659</t>
+          <t>121577</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>113239</t>
+          <t>118801</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>116246</t>
+          <t>122179</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>365947</t>
+          <t>376113</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>358261</t>
+          <t>367409</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>369484</t>
+          <t>379606</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,66%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>254456</t>
+          <t>258711</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>254456</t>
+          <t>258711</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>254456</t>
+          <t>258711</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>116246</t>
+          <t>122179</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>116246</t>
+          <t>122179</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>116246</t>
+          <t>122179</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>370703</t>
+          <t>380889</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>370703</t>
+          <t>380889</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>370703</t>
+          <t>380889</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>18709</t>
+          <t>23630</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11659</t>
+          <t>15617</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28030</t>
+          <t>34057</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2247</t>
+          <t>2285</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>606</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5887</t>
+          <t>5309</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>20957</t>
+          <t>25915</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13392</t>
+          <t>16444</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30572</t>
+          <t>37242</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>13,47%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>166477</t>
+          <t>163683</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>157156</t>
+          <t>153256</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>173527</t>
+          <t>171696</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>88025</t>
+          <t>86926</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>84385</t>
+          <t>83902</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>89665</t>
+          <t>88605</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>254501</t>
+          <t>250608</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>244886</t>
+          <t>239281</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>262066</t>
+          <t>260079</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>94,05%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>185186</t>
+          <t>187313</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>185186</t>
+          <t>187313</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>185186</t>
+          <t>187313</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>90272</t>
+          <t>89211</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>90272</t>
+          <t>89211</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>90272</t>
+          <t>89211</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>276523</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>276523</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>276523</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8330</t>
+          <t>8636</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3586</t>
+          <t>3857</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15696</t>
+          <t>16772</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>979</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -11771,12 +11771,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3021</t>
+          <t>3633</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -11786,7 +11786,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>9233</t>
+          <t>9614</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4419</t>
+          <t>4755</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16912</t>
+          <t>19491</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>169848</t>
+          <t>194800</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>162482</t>
+          <t>186664</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>174592</t>
+          <t>199579</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,27 +11874,27 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>123443</t>
+          <t>137387</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>121324</t>
+          <t>134733</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>124345</t>
+          <t>138366</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>293291</t>
+          <t>332188</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>285612</t>
+          <t>322311</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>298105</t>
+          <t>337047</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,61%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>178178</t>
+          <t>203436</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>178178</t>
+          <t>203436</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>178178</t>
+          <t>203436</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>124345</t>
+          <t>138366</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>124345</t>
+          <t>138366</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>124345</t>
+          <t>138366</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>302524</t>
+          <t>341802</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>302524</t>
+          <t>341802</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>302524</t>
+          <t>341802</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12104,7 +12104,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>469</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -12114,12 +12114,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2046</t>
+          <t>2560</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -12129,7 +12129,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>469</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -12149,12 +12149,12 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2490</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -12182,7 +12182,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>31146</t>
+          <t>34137</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -12217,27 +12217,27 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8143</t>
+          <t>10376</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6537</t>
+          <t>8285</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>10845</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -12252,27 +12252,27 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>39289</t>
+          <t>44513</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37239</t>
+          <t>42510</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>39729</t>
+          <t>44982</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>31146</t>
+          <t>34137</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31146</t>
+          <t>34137</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>31146</t>
+          <t>34137</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>10845</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>10845</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>10845</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>39729</t>
+          <t>44982</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>39729</t>
+          <t>44982</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>39729</t>
+          <t>44982</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9662</t>
+          <t>9208</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4902</t>
+          <t>5138</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16056</t>
+          <t>15827</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>2838</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>615</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6260</t>
+          <t>7070</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>12039</t>
+          <t>12046</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6482</t>
+          <t>7038</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18566</t>
+          <t>19018</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>155386</t>
+          <t>153765</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>148992</t>
+          <t>147146</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>160146</t>
+          <t>157835</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>94043</t>
+          <t>95356</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>90160</t>
+          <t>91124</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>95691</t>
+          <t>97579</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>249429</t>
+          <t>249121</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>242902</t>
+          <t>242149</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>254986</t>
+          <t>254129</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,31%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>165048</t>
+          <t>162973</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>165048</t>
+          <t>162973</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>165048</t>
+          <t>162973</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>96420</t>
+          <t>98194</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>96420</t>
+          <t>98194</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>96420</t>
+          <t>98194</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>261468</t>
+          <t>261167</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>261468</t>
+          <t>261167</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>261468</t>
+          <t>261167</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>41876</t>
+          <t>49594</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>29682</t>
+          <t>35064</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>62744</t>
+          <t>66542</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>14591</t>
+          <t>20355</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2867</t>
+          <t>12145</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35268</t>
+          <t>32133</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>56467</t>
+          <t>69949</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>26236</t>
+          <t>53033</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>89247</t>
+          <t>91218</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>15,6%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>266054</t>
+          <t>300111</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>245186</t>
+          <t>283163</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>278248</t>
+          <t>314641</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>385693</t>
+          <t>214695</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>365016</t>
+          <t>202917</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>397417</t>
+          <t>222905</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>651747</t>
+          <t>514806</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>618967</t>
+          <t>493537</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>681978</t>
+          <t>531722</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>90,93%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>307930</t>
+          <t>349705</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>307930</t>
+          <t>349705</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>307930</t>
+          <t>349705</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>400284</t>
+          <t>235050</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>400284</t>
+          <t>235050</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>400284</t>
+          <t>235050</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708214</t>
+          <t>584755</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708214</t>
+          <t>584755</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708214</t>
+          <t>584755</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>6407</t>
+          <t>7077</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2684</t>
+          <t>3004</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12351</t>
+          <t>14140</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3342</t>
+          <t>3719</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>809</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>9750</t>
+          <t>10797</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4785</t>
+          <t>5647</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>17143</t>
+          <t>20260</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>271130</t>
+          <t>307259</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>265186</t>
+          <t>300196</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>274853</t>
+          <t>311332</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>96483</t>
+          <t>111235</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>91161</t>
+          <t>105953</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>98835</t>
+          <t>114145</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>367612</t>
+          <t>418492</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>360219</t>
+          <t>409029</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>372577</t>
+          <t>423642</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>277537</t>
+          <t>314336</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>277537</t>
+          <t>314336</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>277537</t>
+          <t>314336</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>99825</t>
+          <t>114954</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>99825</t>
+          <t>114954</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>99825</t>
+          <t>114954</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>377362</t>
+          <t>429289</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>377362</t>
+          <t>429289</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>377362</t>
+          <t>429289</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>97735</t>
+          <t>109186</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>77979</t>
+          <t>87427</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>121734</t>
+          <t>134739</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>24487</t>
+          <t>31247</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>12493</t>
+          <t>21744</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>37468</t>
+          <t>45524</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>122222</t>
+          <t>140433</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>93197</t>
+          <t>118684</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>150627</t>
+          <t>169199</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,54%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1481636</t>
+          <t>1571323</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1457637</t>
+          <t>1545770</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1501392</t>
+          <t>1593082</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1002172</t>
+          <t>874782</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>989191</t>
+          <t>860505</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1014166</t>
+          <t>884285</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>2483807</t>
+          <t>2446105</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2455402</t>
+          <t>2417339</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2512832</t>
+          <t>2467854</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>95,41%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1579371</t>
+          <t>1680509</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1579371</t>
+          <t>1680509</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1579371</t>
+          <t>1680509</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1026659</t>
+          <t>906029</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1026659</t>
+          <t>906029</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1026659</t>
+          <t>906029</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>2606029</t>
+          <t>2586538</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2606029</t>
+          <t>2586538</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2606029</t>
+          <t>2586538</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
